--- a/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,6 +966,138 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Position Hierarchy Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Developer Mode</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cache Handling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Position Hierarchy Settings</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -991,73 +991,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Developer Mode</t>
+          <t>Position Hierarchy Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>h_01M3K9HRXCQ8BCQH1JZ7Y86FSE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3K9HRXCQ8BCQH1JZ7Y86FSE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cache Handling</t>
+          <t>Developer Mode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Cache Handling</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>h_01K06FVR3HAYYM66WATF77B0B4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K06FVR3HAYYM66WATF77B0B4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,63 +495,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01M39P83NDFB4NK54H661Q11W9</t>
+          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39P83NDFB4NK54H661Q11W9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01M39PK611M7BR7E632PAVKN9M</t>
+          <t>h_01M39P83NDFB4NK54H661Q11W9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39PK611M7BR7E632PAVKN9M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39P83NDFB4NK54H661Q11W9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01M39PVCBS473R4RN8Q65FDKVP</t>
+          <t>h_01M39PK611M7BR7E632PAVKN9M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39PVCBS473R4RN8Q65FDKVP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39PK611M7BR7E632PAVKN9M</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
+          <t>h_01M39PVCBS473R4RN8Q65FDKVP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M39PVCBS473R4RN8Q65FDKVP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Execution Features</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
+          <t>h_01M3KJ2XCRK66AZG4QSQ1HYGPJ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3KJ2XCRK66AZG4QSQ1HYGPJ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
+          <t>h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
+          <t>h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
+          <t>h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,63 +693,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01M3BMD27MBG166NPT9RRJS3ZN</t>
+          <t>h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMD27MBG166NPT9RRJS3ZN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Template For User Creation</t>
+          <t>Notification Setting</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
+          <t>h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Insights Setting</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
+          <t>h_01M3BMD27MBG166NPT9RRJS3ZN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMD27MBG166NPT9RRJS3ZN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Template For User Creation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,85 +759,85 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
+          <t>h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insights Setting</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01M3BWAD5MS8J3928022JXEY2W</t>
+          <t>h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWAD5MS8J3928022JXEY2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
+          <t>h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
+          <t>h_01M3BWAD5MS8J3928022JXEY2W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWAD5MS8J3928022JXEY2W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
+          <t>h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
+          <t>h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
+          <t>h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Position Sync Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01M3BXY85YE7BY40CFH40BJ7ER</t>
+          <t>h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BXY85YE7BY40CFH40BJ7ER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manager Assignment Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01M3BY46TPGAX117KEGJ9HSXM0</t>
+          <t>h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BY46TPGAX117KEGJ9HSXM0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Position Sync Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
+          <t>h_01M3BXY85YE7BY40CFH40BJ7ER</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BXY85YE7BY40CFH40BJ7ER</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Manager Assignment Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+          <t>h_01M3BY46TPGAX117KEGJ9HSXM0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BY46TPGAX117KEGJ9HSXM0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Position Hierarchy Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M3K9HRXCQ8BCQH1JZ7Y86FSE</t>
+          <t>h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3K9HRXCQ8BCQH1JZ7Y86FSE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Developer Mode</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cache Handling</t>
+          <t>Position Hierarchy Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,56 +1045,122 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Developer Mode</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Cache Handling</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Connections</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Execution Features</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,85 +605,85 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01M3KJ2XCRK66AZG4QSQ1HYGPJ</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3KJ2XCRK66AZG4QSQ1HYGPJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
+          <t>h_01M4D01N1MBVPXMD7TJ2E2CZ88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M4D01N1MBVPXMD7TJ2E2CZ88</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
+          <t>h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQQT3HF63HZG3F8FGP5C7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
+          <t>h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
+          <t>h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQQ27WK4ZAMGBXCRWJDFX6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Position Sync Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
+          <t>h_01M3BXY85YE7BY40CFH40BJ7ER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BXY85YE7BY40CFH40BJ7ER</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Manager Assignment Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01M3BMD27MBG166NPT9RRJS3ZN</t>
+          <t>h_01M3BY46TPGAX117KEGJ9HSXM0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMD27MBG166NPT9RRJS3ZN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BY46TPGAX117KEGJ9HSXM0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Template For User Creation</t>
+          <t>Position Hierarchy Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
+          <t>h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Setting</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
+          <t>h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
+          <t>h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BQ9J5PNQS7EHWYFC3JAEG8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01M3BWAD5MS8J3928022JXEY2W</t>
+          <t>h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWAD5MS8J3928022JXEY2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BAQ2PQ6H6W5BQG9YDFHG7C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
+          <t>h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWDR7H5N5RTGWK5J0YSDK9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BFK7YXV0R48025Z5QM7ZVW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
+          <t>h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWEHTQCKVYEGQND8TXQ7HG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BGWM2CKHB6H4KBS4ZZY94A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
+          <t>h_01M3BMD27MBG166NPT9RRJS3ZN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWP5S4CT3YKFSZC8B5BEN6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMD27MBG166NPT9RRJS3ZN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Notification Template For User Creation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,254 +913,232 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
+          <t>h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWTBZG65YXBB8X6DW8FG8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BMEBXGDZ09NF3JZ7CTY3QA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
+          <t>h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BWXCBY8YB2WAFS94TDGSDX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BKZN7YQZ4C8NEV6KW1ZP3Y</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Position Sync Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M3BXY85YE7BY40CFH40BJ7ER</t>
+          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BXY85YE7BY40CFH40BJ7ER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Manager Assignment Settings</t>
+          <t>Employee sync</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M3BY46TPGAX117KEGJ9HSXM0</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BY46TPGAX117KEGJ9HSXM0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Department sync</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
+          <t>h_01M47ZTVW5RJHC15B4FWWEC3GC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3BZQNJPKE56WS0VZVXQTWVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M47ZTVW5RJHC15B4FWWEC3GC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Job sync</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
+          <t>h_01M47ZTZYCKMDKEGC3TDSZAQE8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3KKXCVY4RMRRJFQFWR5MZ13</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M47ZTZYCKMDKEGC3TDSZAQE8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Position Hierarchy Settings</t>
+          <t>Position sync</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+          <t>h_01M47ZV3EVTSN7DW2BD8FHJSQF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C81VZ70Y77FDK2DPJFP0JT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M47ZV3EVTSN7DW2BD8FHJSQF</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Developer Mode</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C86A3HJCXRVV3N6NG6RW7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cache Handling</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C87AVMWY87WSHFG1VAHNS5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8A6B2XHM3T1AESRES74J8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01M3C8AGQXA81YXJWKBXKD7SY2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Dynamics-365-Finance-and-Operations-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
